--- a/templates/export_template.xlsx
+++ b/templates/export_template.xlsx
@@ -11,6 +11,7 @@
     <sheet name="W2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="W3" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="W4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="模板说明" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1438,13 +1439,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:XFD500"/>
+  <dimension ref="A1:XFD39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" s="6">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>综合绩效</t>
+          <t>综合绩效（兼容：新版按周质检修正 / 老版按月不修正）</t>
         </is>
       </c>
       <c r="B1" s="33" t="n"/>
@@ -35089,466 +35090,6 @@
       <c r="S39" s="42" t="n"/>
     </row>
     <row r="40" s="6"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="E2:G2"/>
@@ -35568,7 +35109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="17" customHeight="1" s="6">
@@ -35869,476 +35410,6 @@
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="5" t="n"/>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
@@ -36353,7 +35424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="17" customHeight="1" s="6">
@@ -36654,476 +35725,6 @@
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="5" t="n"/>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
@@ -37138,7 +35739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="9.5" customWidth="1" style="6" min="6" max="6"/>
@@ -37451,475 +36052,6 @@
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="5" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
@@ -37934,7 +36066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="9.5" customWidth="1" style="6" min="4" max="4"/>
@@ -38247,479 +36379,59 @@
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="5" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>导出模板说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. 新版客服：按周维度计算（质检A/B/C + 质检会话占比修正）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2. 老版客服：按月维度计算（不做质检修正），月度达成率=月总工时/10560。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3. 老版超激励：10800分钟起，按每240分钟递增75，封顶1525。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4. 导出结果会附带核验工作表：核验_工单导入、核验_QA导入。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>